--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4672A731-916C-496D-BFD1-5494DEAF6F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3501963C-7886-47AC-82FA-21520AD63876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="672" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>Mixer</t>
+  </si>
+  <si>
+    <t>当前语言</t>
+  </si>
+  <si>
+    <t>Language</t>
   </si>
 </sst>
 </file>
@@ -396,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -433,6 +439,14 @@
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3501963C-7886-47AC-82FA-21520AD63876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF945F2-CCBB-4E99-A8BB-80AACDDF089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="672" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5184" yWindow="1020" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -82,6 +82,57 @@
   </si>
   <si>
     <t>Language</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>玩家疾跑</t>
+  </si>
+  <si>
+    <t>暂停/返回</t>
+  </si>
+  <si>
+    <t>Pause</t>
+  </si>
+  <si>
+    <t>Interact</t>
+  </si>
+  <si>
+    <t>物体交互</t>
+  </si>
+  <si>
+    <t>对话推进</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+  </si>
+  <si>
+    <t>移动速度</t>
+  </si>
+  <si>
+    <t>疾跑速度</t>
+  </si>
+  <si>
+    <t>人物设定</t>
+  </si>
+  <si>
+    <t>Player Settings</t>
+  </si>
+  <si>
+    <t>按键设定</t>
+  </si>
+  <si>
+    <t>Key Bindings</t>
+  </si>
+  <si>
+    <t>正在为&lt;color=#FFC600&gt;{action}&lt;/color&gt;重新绑定，当前按键：&lt;color=#FFC600&gt;{key}&lt;/color&gt;\n请按任意键设置新按键\n提示：如果 {key} 已被其他操作使用，此次更改将不会应用</t>
+  </si>
+  <si>
+    <t>Rebinding &lt;color=#FFC600&gt;{action}&lt;/color&gt; Current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to assign a new binding.\nNote: if {key} is already assigned to another action, this change will not be applied.</t>
+  </si>
+  <si>
+    <t>Speed</t>
   </si>
 </sst>
 </file>
@@ -402,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -447,6 +498,78 @@
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF945F2-CCBB-4E99-A8BB-80AACDDF089C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B339882-8262-4E0C-BB2C-878D7DC92F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5184" yWindow="1020" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="672" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -133,6 +133,30 @@
   </si>
   <si>
     <t>Speed</t>
+  </si>
+  <si>
+    <t>文本速率</t>
+  </si>
+  <si>
+    <t>Text Speed</t>
+  </si>
+  <si>
+    <t>恢复默认</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>系统设定</t>
+  </si>
+  <si>
+    <t>System Settings</t>
+  </si>
+  <si>
+    <t>音量设定</t>
+  </si>
+  <si>
+    <t>Audio Settings</t>
   </si>
 </sst>
 </file>
@@ -453,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -570,6 +594,38 @@
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B339882-8262-4E0C-BB2C-878D7DC92F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9285633-7476-4724-A247-F4510D7196A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="672" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7644" yWindow="1140" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -157,6 +157,60 @@
   </si>
   <si>
     <t>Audio Settings</t>
+  </si>
+  <si>
+    <t>分辨率</t>
+  </si>
+  <si>
+    <t>Resolution</t>
+  </si>
+  <si>
+    <t>显示模式</t>
+  </si>
+  <si>
+    <t>窗口化</t>
+  </si>
+  <si>
+    <t>Windowed</t>
+  </si>
+  <si>
+    <t>全屏</t>
+  </si>
+  <si>
+    <t>Full Screen</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>Settings</t>
+  </si>
+  <si>
+    <t>背包</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>物品列表</t>
+  </si>
+  <si>
+    <t>硬币</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
+    <t>日记</t>
+  </si>
+  <si>
+    <t>Journal</t>
+  </si>
+  <si>
+    <t>Item List</t>
+  </si>
+  <si>
+    <t>Display Mode</t>
   </si>
 </sst>
 </file>
@@ -477,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="67.21875" customWidth="1"/>
@@ -626,6 +680,78 @@
       </c>
       <c r="B18" s="1" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9285633-7476-4724-A247-F4510D7196A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E0E8CC-6BBA-4BC5-8E91-F6C53BF41BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7644" yWindow="1140" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="996" yWindow="2520" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -126,12 +126,6 @@
     <t>Key Bindings</t>
   </si>
   <si>
-    <t>正在为&lt;color=#FFC600&gt;{action}&lt;/color&gt;重新绑定，当前按键：&lt;color=#FFC600&gt;{key}&lt;/color&gt;\n请按任意键设置新按键\n提示：如果 {key} 已被其他操作使用，此次更改将不会应用</t>
-  </si>
-  <si>
-    <t>Rebinding &lt;color=#FFC600&gt;{action}&lt;/color&gt; Current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to assign a new binding.\nNote: if {key} is already assigned to another action, this change will not be applied.</t>
-  </si>
-  <si>
     <t>Speed</t>
   </si>
   <si>
@@ -211,6 +205,12 @@
   </si>
   <si>
     <t>Display Mode</t>
+  </si>
+  <si>
+    <t>正在为&lt;color=#FFC600&gt;{action}&lt;/color&gt;重新绑定，当前按键：&lt;color=#FFC600&gt;{key}&lt;/color&gt;\n请按任意键设置新按键\n提示：如果{key}已被其他操作使用，或者修改的按键为WASD或方向键（↑↓←→）此次更改将不会应用</t>
+  </si>
+  <si>
+    <t>Rebinding for &lt;color=#FFC600&gt;{action}&lt;/color&gt;, current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to set a new key\nTip: If {key} is already used by another action, or if the key being changed is WASD or the arrow keys (↑↓←→), this change will not be applied</t>
   </si>
 </sst>
 </file>
@@ -534,7 +534,7 @@
   <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="67.21875" customWidth="1"/>
+    <col min="1" max="1" width="80.44140625" customWidth="1"/>
     <col min="2" max="2" width="67.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -615,7 +615,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -642,116 +642,116 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E0E8CC-6BBA-4BC5-8E91-F6C53BF41BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4C2C9-20EF-4B96-841C-B6A1D87BE954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="996" yWindow="2520" windowWidth="19512" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5808" yWindow="1956" windowWidth="16848" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
   <si>
     <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
 This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
@@ -211,6 +211,24 @@
   </si>
   <si>
     <t>Rebinding for &lt;color=#FFC600&gt;{action}&lt;/color&gt;, current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to set a new key\nTip: If {key} is already used by another action, or if the key being changed is WASD or the arrow keys (↑↓←→), this change will not be applied</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>要购买吗？</t>
+  </si>
+  <si>
+    <t>Ready to buy?</t>
   </si>
 </sst>
 </file>
@@ -531,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -752,6 +770,30 @@
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A4C2C9-20EF-4B96-841C-B6A1D87BE954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F0527D-3BAF-4BBE-B166-1486E6BE02B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5808" yWindow="1956" windowWidth="16848" windowHeight="11568" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3408" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">'1-Scene-1'!#REF!</definedName>
@@ -37,22 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
-  <si>
-    <t>All storylines and characters in this work are &lt;color=#FF0000&gt;fictional&lt;/color&gt;; any resemblance to actual persons or events is purely coincidental.
-This work contains &lt;color=#FF0000&gt;mild violence and tense&lt;/color&gt; scenes, and is recommended for players aged 12 and up.
-&lt;color=#FFCC00&gt;Game Tip: Press Space or click to continue the dialogue&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>本作のストーリーおよびキャラクターはすべて&lt;color=#FF0000&gt;フィクション&lt;/color&gt;であり、実在の人物や出来事との類似は純粋に偶然のものです。
-本作には&lt;color=#FF0000&gt;軽度の暴力表現および緊張感のある&lt;/color&gt;シーンが含まれており、12歳以上のプレイヤーにおすすめします。
-&lt;color=#FFCC00&gt;ゲームヒント：スペースキーを押すかクリックして会話を進めてください&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>本作所有剧情与角色均为&lt;color=#FF0000&gt;虚构&lt;/color&gt;，如有雷同，实属巧合
-本作含有&lt;color=#FF0000&gt;轻微暴力及紧张&lt;/color&gt;场面，建议 12 岁以上玩家游玩
-&lt;color=#FFCC00&gt;游戏提示：按空格或点击继续对话&lt;/color&gt;</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
   <si>
     <t>zh</t>
   </si>
@@ -229,6 +213,66 @@
   </si>
   <si>
     <t>Ready to buy?</t>
+  </si>
+  <si>
+    <t>{yyyy}年{MM}月{dd}日 {period}{hh}点{mm}分</t>
+  </si>
+  <si>
+    <t>上午</t>
+  </si>
+  <si>
+    <t>AM</t>
+  </si>
+  <si>
+    <t>下午</t>
+  </si>
+  <si>
+    <t>PM</t>
+  </si>
+  <si>
+    <t>凌晨</t>
+  </si>
+  <si>
+    <t>夜间</t>
+  </si>
+  <si>
+    <t>{MM}/{dd}/{yyyy} {hh}:{mm} {period}</t>
+  </si>
+  <si>
+    <t>抵达天台</t>
+  </si>
+  <si>
+    <t>探索天台</t>
+  </si>
+  <si>
+    <t>Arrival</t>
+  </si>
+  <si>
+    <t>Exploration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总算溜上来了: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">·爬六层楼差点要命，在五楼还差点撞见主任 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">·我决定用石头卡住铁门，要是被风刮得锁上就完了 </t>
+  </si>
+  <si>
+    <t>·Climbing six flights nearly killed me; I almost ran into the dean on the fifth floor.</t>
+  </si>
+  <si>
+    <t>·I decided to wedge the iron door with a rock—if the wind blows it shut and it locks, I’m done for.</t>
+  </si>
+  <si>
+    <t>·Since I’m up here, let’s follow the footprints and check that &lt;color=#FFC600&gt;notice board&lt;/color&gt; up ahead.</t>
+  </si>
+  <si>
+    <t>Finally snuck up here:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">·既然上来了，先跟着脚印去前面那个&lt;color=#FFC600&gt;告示牌&lt;/color&gt;看看吧 </t>
   </si>
 </sst>
 </file>
@@ -549,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -558,267 +602,330 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="41.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F0527D-3BAF-4BBE-B166-1486E6BE02B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD57CA3C-A39B-4CD1-B2D5-214889A48A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3408" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4752" yWindow="3096" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>zh</t>
   </si>
@@ -239,40 +239,10 @@
     <t>{MM}/{dd}/{yyyy} {hh}:{mm} {period}</t>
   </si>
   <si>
-    <t>抵达天台</t>
-  </si>
-  <si>
-    <t>探索天台</t>
-  </si>
-  <si>
-    <t>Arrival</t>
-  </si>
-  <si>
-    <t>Exploration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">总算溜上来了: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">·爬六层楼差点要命，在五楼还差点撞见主任 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">·我决定用石头卡住铁门，要是被风刮得锁上就完了 </t>
-  </si>
-  <si>
-    <t>·Climbing six flights nearly killed me; I almost ran into the dean on the fifth floor.</t>
-  </si>
-  <si>
-    <t>·I decided to wedge the iron door with a rock—if the wind blows it shut and it locks, I’m done for.</t>
-  </si>
-  <si>
-    <t>·Since I’m up here, let’s follow the footprints and check that &lt;color=#FFC600&gt;notice board&lt;/color&gt; up ahead.</t>
-  </si>
-  <si>
-    <t>Finally snuck up here:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">·既然上来了，先跟着脚印去前面那个&lt;color=#FFC600&gt;告示牌&lt;/color&gt;看看吧 </t>
+    <t>总算溜上来了！这趟真是惊险，不仅爬楼累个半死，还险些在五楼和主任撞个正着。当务之急是用石头卡好铁门，万一被风吹得锁上可就麻烦大了</t>
+  </si>
+  <si>
+    <t>刚刚检查完告示牌，但我感觉这里有些说不上的变化。看来得认真&lt;color=#FFC600&gt;调查&lt;/color&gt;一下这里了：左边那片草甸、长势迥异的盆栽，还有保洁工具和除草剂的奇怪组合，都得仔细看看</t>
   </si>
 </sst>
 </file>
@@ -593,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -880,53 +850,20 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36" s="1"/>
+    </row>
+    <row r="37" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="B37" s="1"/>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B40" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" t="s">
-        <v>76</v>
-      </c>
+      <c r="A38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD57CA3C-A39B-4CD1-B2D5-214889A48A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2698CA89-2DB3-46BE-BDED-94741B3C9809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4752" yWindow="3096" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5064" yWindow="2736" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>zh</t>
   </si>
@@ -239,10 +239,136 @@
     <t>{MM}/{dd}/{yyyy} {hh}:{mm} {period}</t>
   </si>
   <si>
-    <t>总算溜上来了！这趟真是惊险，不仅爬楼累个半死，还险些在五楼和主任撞个正着。当务之急是用石头卡好铁门，万一被风吹得锁上可就麻烦大了</t>
-  </si>
-  <si>
-    <t>刚刚检查完告示牌，但我感觉这里有些说不上的变化。看来得认真&lt;color=#FFC600&gt;调查&lt;/color&gt;一下这里了：左边那片草甸、长势迥异的盆栽，还有保洁工具和除草剂的奇怪组合，都得仔细看看</t>
+    <t>日记已更新</t>
+  </si>
+  <si>
+    <t>Journal Updated</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>抵达天台</t>
+  </si>
+  <si>
+    <t>Arrival</t>
+  </si>
+  <si>
+    <t>探索天台</t>
+  </si>
+  <si>
+    <t>Explore</t>
+  </si>
+  <si>
+    <t>售货机？</t>
+  </si>
+  <si>
+    <t>我总感觉天台上有些说不上来的变化：</t>
+  </si>
+  <si>
+    <t>·左侧杂乱的&lt;color=#FFC600&gt;草甸&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>·三盆长势不同的&lt;color=#FFC600&gt;盆栽&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>·旁边的&lt;color=#FFC600&gt;保洁工具和除草剂&lt;/color&gt;组合</t>
+  </si>
+  <si>
+    <t>重点搜索一下这些地方吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">总算溜上来了: </t>
+  </si>
+  <si>
+    <t>·我决定用石头卡住铁门，要是被风刮得锁上就完了</t>
+  </si>
+  <si>
+    <t>·既然上来了，先跟着脚印去前面那个&lt;color=#FFC600&gt;告示牌&lt;/color&gt;看看吧</t>
+  </si>
+  <si>
+    <t>·这趟真是惊险，险些在五楼和主任撞个正着，我决定用石头卡住铁门，要是被风刮得锁上就完了</t>
+  </si>
+  <si>
+    <t>Drink?</t>
+  </si>
+  <si>
+    <t>天台上的售货机？正好我有点渴了：</t>
+  </si>
+  <si>
+    <t>·&lt;color=#FFC600&gt;下水道&lt;/color&gt;里那枚硬币，呃，看来得克服一下了</t>
+  </si>
+  <si>
+    <t>·草甸旁的&lt;color=#FFC600&gt;石头&lt;/color&gt;说不定有什么</t>
+  </si>
+  <si>
+    <t>·右边的&lt;color=#FFC600&gt;石缝&lt;/color&gt;里好像闪烁着银光</t>
+  </si>
+  <si>
+    <t>看来需要收集到三枚硬币</t>
+  </si>
+  <si>
+    <t>I keep feeling there are some indescribable changes on the rooftop:</t>
+  </si>
+  <si>
+    <t>· the messy &lt;color=#FFC600&gt;meadow&lt;/color&gt; on the left</t>
+  </si>
+  <si>
+    <t>· three &lt;color=#FFC600&gt;potted plants&lt;/color&gt; with different growth</t>
+  </si>
+  <si>
+    <t>· the nearby set of &lt;color=#FFC600&gt;cleaning tools and herbicide&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Let’s focus on searching these places!</t>
+  </si>
+  <si>
+    <t>Finally slipped up here:</t>
+  </si>
+  <si>
+    <t>· this trip was really thrilling; I almost ran right into the director on the fifth floor. I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over</t>
+  </si>
+  <si>
+    <t>· I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over</t>
+  </si>
+  <si>
+    <t>· since I’m up here, I’ll follow the footprints to that &lt;color=#FFC600&gt;notice board&lt;/color&gt; up ahead and take a look</t>
+  </si>
+  <si>
+    <t>A vending machine on the rooftop? Just right, I’m a bit thirsty:</t>
+  </si>
+  <si>
+    <t>· that coin in the &lt;color=#FFC600&gt;sewer&lt;/color&gt;—uh, looks like I’ll have to get over it</t>
+  </si>
+  <si>
+    <t>· the &lt;color=#FFC600&gt;stone&lt;/color&gt; by the meadow might have something</t>
+  </si>
+  <si>
+    <t>· there seems to be a silvery glint in the &lt;color=#FFC600&gt;rock crevice&lt;/color&gt; on the right</t>
+  </si>
+  <si>
+    <t>Looks like I need to collect three coins.</t>
+  </si>
+  <si>
+    <t>任务详情会显示在这里\n（点击任意处关闭当前教程）\n↓</t>
+  </si>
+  <si>
+    <t>点击探索天台\n↓</t>
+  </si>
+  <si>
+    <t>点击日记\n↓</t>
+  </si>
+  <si>
+    <t>Task details will be displayed here\n(Click anywhere to close the current tutorial)\n↓</t>
+  </si>
+  <si>
+    <t>Click Journal\n↓</t>
+  </si>
+  <si>
+    <t>Click Explore\n↓</t>
   </si>
 </sst>
 </file>
@@ -563,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -850,20 +976,181 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B43" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2698CA89-2DB3-46BE-BDED-94741B3C9809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7059B433-8101-41A9-A66A-C8651EA769F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5064" yWindow="2736" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2760" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
   <si>
     <t>zh</t>
   </si>
@@ -59,9 +59,6 @@
     <t>BGM</t>
   </si>
   <si>
-    <t>Mixer</t>
-  </si>
-  <si>
     <t>当前语言</t>
   </si>
   <si>
@@ -194,9 +191,6 @@
     <t>正在为&lt;color=#FFC600&gt;{action}&lt;/color&gt;重新绑定，当前按键：&lt;color=#FFC600&gt;{key}&lt;/color&gt;\n请按任意键设置新按键\n提示：如果{key}已被其他操作使用，或者修改的按键为WASD或方向键（↑↓←→）此次更改将不会应用</t>
   </si>
   <si>
-    <t>Rebinding for &lt;color=#FFC600&gt;{action}&lt;/color&gt;, current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to set a new key\nTip: If {key} is already used by another action, or if the key being changed is WASD or the arrow keys (↑↓←→), this change will not be applied</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
     <t>要购买吗？</t>
   </si>
   <si>
-    <t>Ready to buy?</t>
-  </si>
-  <si>
     <t>{yyyy}年{MM}月{dd}日 {period}{hh}点{mm}分</t>
   </si>
   <si>
@@ -281,9 +272,6 @@
     <t>重点搜索一下这些地方吧！</t>
   </si>
   <si>
-    <t xml:space="preserve">总算溜上来了: </t>
-  </si>
-  <si>
     <t>·我决定用石头卡住铁门，要是被风刮得锁上就完了</t>
   </si>
   <si>
@@ -341,15 +329,9 @@
     <t>A vending machine on the rooftop? Just right, I’m a bit thirsty:</t>
   </si>
   <si>
-    <t>· that coin in the &lt;color=#FFC600&gt;sewer&lt;/color&gt;—uh, looks like I’ll have to get over it</t>
-  </si>
-  <si>
     <t>· the &lt;color=#FFC600&gt;stone&lt;/color&gt; by the meadow might have something</t>
   </si>
   <si>
-    <t>· there seems to be a silvery glint in the &lt;color=#FFC600&gt;rock crevice&lt;/color&gt; on the right</t>
-  </si>
-  <si>
     <t>Looks like I need to collect three coins.</t>
   </si>
   <si>
@@ -369,6 +351,30 @@
   </si>
   <si>
     <t>Click Explore\n↓</t>
+  </si>
+  <si>
+    <t>总算溜上来了:</t>
+  </si>
+  <si>
+    <t>开始游戏</t>
+  </si>
+  <si>
+    <t>Start Game</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Rebinding for &lt;color=#FFC600&gt;{action}&lt;/color&gt;, current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to set a new binding\nTip: If {key} is already used by another action, or if the key being changed is WASD or the arrow keys (↑↓←→), this change will not be applied</t>
+  </si>
+  <si>
+    <t>· that coin in the &lt;color=#FFC600&gt;storm drain&lt;/color&gt;—uh, looks like I’ll have to get over it</t>
+  </si>
+  <si>
+    <t>· there seems to be a silvery glint in the &lt;color=#FFC600&gt;stone crevice&lt;/color&gt; on the right</t>
+  </si>
+  <si>
+    <t>Buy now?</t>
   </si>
 </sst>
 </file>
@@ -689,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -704,452 +710,460 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B41" t="s">
-        <v>91</v>
+        <v>72</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>105</v>
+      <c r="A55" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="1" t="s">
-        <v>106</v>
+      <c r="A56" t="s">
+        <v>99</v>
       </c>
       <c r="B56" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B58" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7059B433-8101-41A9-A66A-C8651EA769F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C103866C-6057-410A-B062-C64A954E0B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2760" windowWidth="17076" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3408" yWindow="2268" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
   <si>
     <t>zh</t>
   </si>
@@ -272,9 +272,6 @@
     <t>重点搜索一下这些地方吧！</t>
   </si>
   <si>
-    <t>·我决定用石头卡住铁门，要是被风刮得锁上就完了</t>
-  </si>
-  <si>
     <t>·既然上来了，先跟着脚印去前面那个&lt;color=#FFC600&gt;告示牌&lt;/color&gt;看看吧</t>
   </si>
   <si>
@@ -302,36 +299,15 @@
     <t>I keep feeling there are some indescribable changes on the rooftop:</t>
   </si>
   <si>
-    <t>· the messy &lt;color=#FFC600&gt;meadow&lt;/color&gt; on the left</t>
-  </si>
-  <si>
-    <t>· three &lt;color=#FFC600&gt;potted plants&lt;/color&gt; with different growth</t>
-  </si>
-  <si>
-    <t>· the nearby set of &lt;color=#FFC600&gt;cleaning tools and herbicide&lt;/color&gt;</t>
-  </si>
-  <si>
     <t>Let’s focus on searching these places!</t>
   </si>
   <si>
     <t>Finally slipped up here:</t>
   </si>
   <si>
-    <t>· this trip was really thrilling; I almost ran right into the director on the fifth floor. I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over</t>
-  </si>
-  <si>
-    <t>· I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over</t>
-  </si>
-  <si>
-    <t>· since I’m up here, I’ll follow the footprints to that &lt;color=#FFC600&gt;notice board&lt;/color&gt; up ahead and take a look</t>
-  </si>
-  <si>
     <t>A vending machine on the rooftop? Just right, I’m a bit thirsty:</t>
   </si>
   <si>
-    <t>· the &lt;color=#FFC600&gt;stone&lt;/color&gt; by the meadow might have something</t>
-  </si>
-  <si>
     <t>Looks like I need to collect three coins.</t>
   </si>
   <si>
@@ -368,13 +344,73 @@
     <t>Rebinding for &lt;color=#FFC600&gt;{action}&lt;/color&gt;, current key: &lt;color=#FFC600&gt;{key}&lt;/color&gt;\nPress any key to set a new binding\nTip: If {key} is already used by another action, or if the key being changed is WASD or the arrow keys (↑↓←→), this change will not be applied</t>
   </si>
   <si>
-    <t>· that coin in the &lt;color=#FFC600&gt;storm drain&lt;/color&gt;—uh, looks like I’ll have to get over it</t>
-  </si>
-  <si>
-    <t>· there seems to be a silvery glint in the &lt;color=#FFC600&gt;stone crevice&lt;/color&gt; on the right</t>
-  </si>
-  <si>
     <t>Buy now?</t>
+  </si>
+  <si>
+    <t>我现在感觉糟透了：</t>
+  </si>
+  <si>
+    <t>·&lt;color=#FFC600&gt;草甸&lt;/color&gt;里的铃兰种球长得怎么样了？……等等，这些草长得都差不多，我有点分不清哪棵是它了</t>
+  </si>
+  <si>
+    <t>·糟了！今天有跑操</t>
+  </si>
+  <si>
+    <t>·真希望这一切只是我的梦</t>
+  </si>
+  <si>
+    <t>完蛋了</t>
+  </si>
+  <si>
+    <t>What?</t>
+  </si>
+  <si>
+    <t>I feel really bad right now:</t>
+  </si>
+  <si>
+    <t>按下ESC查看</t>
+  </si>
+  <si>
+    <t>Press ESC to view</t>
+  </si>
+  <si>
+    <t>重要提醒：此游戏流程约 10 分钟，暂不支持存档/读档，请确保有完整游玩的时间</t>
+  </si>
+  <si>
+    <t>· since I’m up here, I’ll follow the footprints to that &lt;color=#FFC600&gt;notice board&lt;/color&gt; up ahead and take a look.</t>
+  </si>
+  <si>
+    <t>· that coin in the &lt;color=#FFC600&gt;storm drain&lt;/color&gt;—uh, looks like I’ll have to get over it.</t>
+  </si>
+  <si>
+    <t>· the &lt;color=#FFC600&gt;stone&lt;/color&gt; by the meadow might have something.</t>
+  </si>
+  <si>
+    <t>· there seems to be a silvery glint in the &lt;color=#FFC600&gt;stone crevice&lt;/color&gt; on the right.</t>
+  </si>
+  <si>
+    <t>· Oh no! There’s a morning run today.</t>
+  </si>
+  <si>
+    <t>· I really hope this is all just a dream.</t>
+  </si>
+  <si>
+    <t>Important Notice: This game takes about 10 minutes to complete and currently does not support saving/loading. Please ensure you have enough time to finish in one go.</t>
+  </si>
+  <si>
+    <t>· How is the lily-of-the-valley bulb in the &lt;color=#FFC600&gt;meadow&lt;/color&gt; doing? ...Wait, all these grasses look so similar—I can’t quite tell which one it is.</t>
+  </si>
+  <si>
+    <t>· the messy &lt;color=#FFC600&gt;meadow&lt;/color&gt; on the left.</t>
+  </si>
+  <si>
+    <t>· three &lt;color=#FFC600&gt;potted plants&lt;/color&gt; with different growth.</t>
+  </si>
+  <si>
+    <t>· the nearby set of &lt;color=#FFC600&gt;cleaning tools and herbicide&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>· this trip was really thrilling; I almost ran right into the director on the fifth floor. I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over.</t>
   </si>
 </sst>
 </file>
@@ -695,11 +731,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
-    <col min="2" max="2" width="67.44140625" customWidth="1"/>
+    <col min="2" max="2" width="141.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -712,10 +748,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -723,7 +759,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -819,7 +855,7 @@
         <v>50</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -947,7 +983,7 @@
         <v>55</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -1027,7 +1063,7 @@
         <v>72</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -1035,7 +1071,7 @@
         <v>73</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -1043,7 +1079,7 @@
         <v>74</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -1051,7 +1087,7 @@
         <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -1059,7 +1095,7 @@
         <v>76</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -1067,23 +1103,23 @@
         <v>77</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1091,15 +1127,15 @@
         <v>78</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -1107,7 +1143,7 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1115,7 +1151,7 @@
         <v>83</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -1123,7 +1159,7 @@
         <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -1131,39 +1167,87 @@
         <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="1" t="s">
-        <v>86</v>
+      <c r="A55" t="s">
+        <v>91</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>99</v>
+      <c r="A56" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B58" t="s">
-        <v>103</v>
+      <c r="B59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>106</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>110</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>112</v>
+      </c>
+      <c r="B64" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C103866C-6057-410A-B062-C64A954E0B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1D4928-B9B9-4C59-B6EC-62C7A1345CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3408" yWindow="2268" windowWidth="19032" windowHeight="8832" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="132">
   <si>
     <t>zh</t>
   </si>
@@ -107,9 +107,6 @@
     <t>Key Bindings</t>
   </si>
   <si>
-    <t>Speed</t>
-  </si>
-  <si>
     <t>文本速率</t>
   </si>
   <si>
@@ -411,6 +408,30 @@
   </si>
   <si>
     <t>· this trip was really thrilling; I almost ran right into the director on the fifth floor. I decide to wedge the iron door with a stone—if the wind blows it shut, it’s over.</t>
+  </si>
+  <si>
+    <t>进入游戏</t>
+  </si>
+  <si>
+    <t>Enter Game</t>
+  </si>
+  <si>
+    <t>退出游戏</t>
+  </si>
+  <si>
+    <t>Exit Game</t>
+  </si>
+  <si>
+    <t>Run Speed</t>
+  </si>
+  <si>
+    <t>Move Speed</t>
+  </si>
+  <si>
+    <t>返回标题</t>
+  </si>
+  <si>
+    <t>Back</t>
   </si>
 </sst>
 </file>
@@ -731,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -748,10 +769,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
         <v>98</v>
-      </c>
-      <c r="B2" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -759,7 +780,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -823,7 +844,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -831,7 +852,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -850,404 +871,428 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" t="s">
         <v>107</v>
-      </c>
-      <c r="B62" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" t="s">
         <v>110</v>
-      </c>
-      <c r="B63" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B64" t="s">
-        <v>119</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1D4928-B9B9-4C59-B6EC-62C7A1345CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38544C61-6A9D-4C67-A8EA-CBE4F18AA9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6756" yWindow="1212" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
   <si>
     <t>zh</t>
   </si>
@@ -432,6 +432,12 @@
   </si>
   <si>
     <t>Back</t>
+  </si>
+  <si>
+    <t>第一章</t>
+  </si>
+  <si>
+    <t>Chapter 1</t>
   </si>
 </sst>
 </file>
@@ -752,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -1293,6 +1299,14 @@
       </c>
       <c r="B67" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38544C61-6A9D-4C67-A8EA-CBE4F18AA9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCC1E92-3D7B-4A70-B733-A5FA78E82DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6756" yWindow="1212" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="936" yWindow="2088" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>zh</t>
   </si>
@@ -438,6 +438,38 @@
   </si>
   <si>
     <t>Chapter 1</t>
+  </si>
+  <si>
+    <t>Chapter Overview</t>
+  </si>
+  <si>
+    <t>本章概要</t>
+  </si>
+  <si>
+    <t>游玩本章</t>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <t>章节选择</t>
+  </si>
+  <si>
+    <t>Chapter Selection</t>
+  </si>
+  <si>
+    <t>第二章</t>
+  </si>
+  <si>
+    <t>Chapter 2</t>
+  </si>
+  <si>
+    <t>确定要退出游戏并返回标题界面吗？当前游戏进度将会丢失。
+提示：若您只是想关闭暂停菜单，再按一次 ESC 即可返回游戏</t>
+  </si>
+  <si>
+    <t>Are you sure you want to quit the game and return to the title screen? Your current progress will be lost.
+Tip: If you only want to close the pause menu, press ESC again to resume the game.</t>
   </si>
 </sst>
 </file>
@@ -758,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -1307,6 +1339,46 @@
       </c>
       <c r="B68" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCC1E92-3D7B-4A70-B733-A5FA78E82DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B445D2E-90BD-4F57-BCC3-0D6C68D20C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="936" yWindow="2088" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="936" yWindow="1212" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-Scene-1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
     <t>zh</t>
   </si>
@@ -470,6 +470,12 @@
   <si>
     <t>Are you sure you want to quit the game and return to the title screen? Your current progress will be lost.
 Tip: If you only want to close the pause menu, press ESC again to resume the game.</t>
+  </si>
+  <si>
+    <t>结束</t>
+  </si>
+  <si>
+    <t>End</t>
   </si>
 </sst>
 </file>
@@ -790,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -1379,6 +1385,14 @@
       </c>
       <c r="B73" s="1" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Localization/strings.xlsx
+++ b/Assets/StreamingAssets/Localization/strings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FYP\Assets\StreamingAssets\Localization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B445D2E-90BD-4F57-BCC3-0D6C68D20C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54A8500-A0F0-4E8E-87E5-C4D44C49C2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="936" yWindow="1212" windowWidth="16080" windowHeight="11028" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="154">
   <si>
     <t>zh</t>
   </si>
@@ -464,18 +464,40 @@
     <t>Chapter 2</t>
   </si>
   <si>
-    <t>确定要退出游戏并返回标题界面吗？当前游戏进度将会丢失。
-提示：若您只是想关闭暂停菜单，再按一次 ESC 即可返回游戏</t>
-  </si>
-  <si>
-    <t>Are you sure you want to quit the game and return to the title screen? Your current progress will be lost.
-Tip: If you only want to close the pause menu, press ESC again to resume the game.</t>
-  </si>
-  <si>
     <t>结束</t>
   </si>
   <si>
     <t>End</t>
+  </si>
+  <si>
+    <t>This chapter is currently in development and is not yet available to play.</t>
+  </si>
+  <si>
+    <t>本章正在制作中，暂未开放游玩</t>
+  </si>
+  <si>
+    <t>继续游玩</t>
+  </si>
+  <si>
+    <t>Continue</t>
+  </si>
+  <si>
+    <t>本章进度已保存\n建议直接&lt;color=#FFC600&gt;继续游玩&lt;/color&gt;，以保持剧情体验的连贯性\n若选择&lt;color=#FFC600&gt;返回标题&lt;/color&gt;，请注意：当前存档系统仍在完善中，部分功能（如日记、背包）在下次游玩时，可能出现数据不同步的情况</t>
+  </si>
+  <si>
+    <t>Your progress in this chapter has been saved.\nWe recommend selecting &lt;color=#FFC600&gt;Continue&lt;/color&gt; to keep the story experience smooth and uninterrupted. \nIf you choose &lt;color=#FFC600&gt;Back&lt;/color&gt; to Title, please note that the save system is still being improved, and some features (such as the Diary and Inventory) may not sync correctly the next time you play.</t>
+  </si>
+  <si>
+    <t>Are you sure you want to quit the game and return to the title screen? Your current progress will be lost.\n\nTip: If you only want to close the pause menu, press ESC again to resume the game.</t>
+  </si>
+  <si>
+    <t>确认</t>
+  </si>
+  <si>
+    <t>Confirm</t>
+  </si>
+  <si>
+    <t>确定要退出游戏并返回标题界面吗？当前游戏进度将会丢失\n\n提示：若您只是想关闭暂停菜单，再按一次 ESC 即可返回游戏</t>
   </si>
 </sst>
 </file>
@@ -796,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5125BF64-7B82-433D-8FED-955690D00D20}">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80.44140625" customWidth="1"/>
@@ -1379,20 +1401,52 @@
         <v>141</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
         <v>144</v>
       </c>
-      <c r="B74" t="s">
-        <v>145</v>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>146</v>
+      </c>
+      <c r="B76" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
